--- a/ticket_order_forms/021_season_ticket_order_form--ticket_order_forms.xlsx
+++ b/ticket_order_forms/021_season_ticket_order_form--ticket_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'1-4_tickets',_'label':_'1-4_tickets'}</t>
+          <t>1-4_tickets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '1-4 tickets', 'label': '1-4 tickets'}</t>
+          <t>1-4 tickets</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'5-8_tickets',_'label':_'5-8_tickets'}</t>
+          <t>5-8_tickets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '5-8 tickets', 'label': '5-8 tickets'}</t>
+          <t>5-8 tickets</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'9-12_tickets',_'label':_'9-12_tickets'}</t>
+          <t>9-12_tickets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '9-12 tickets', 'label': '9-12 tickets'}</t>
+          <t>9-12 tickets</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'13-16_tickets',_'label':_'13-16_tickets'}</t>
+          <t>13-16_tickets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '13-16 tickets', 'label': '13-16 tickets'}</t>
+          <t>13-16 tickets</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'credit card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
